--- a/public/Plantilla_Usuarios_Casa_Diseno.xlsx
+++ b/public/Plantilla_Usuarios_Casa_Diseno.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/49229b76a1a0683f/DESCARGAS EDMUNDO/GENERADOR DE HONORARIOS/Cotizador_Casa_Diseno_v2.4.0_GitHub_Render/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D9DB6E98-124C-4C9C-B228-8F51223227B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_908C7C1A54C067EE919BC92D2F7CF89471399291" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>nombre_completo</t>
   </si>
@@ -41,18 +41,36 @@
     <t>activo</t>
   </si>
   <si>
+    <t>Juan Pérez</t>
+  </si>
+  <si>
+    <t>juan@empresa.cl</t>
+  </si>
+  <si>
     <t>comercial</t>
   </si>
   <si>
     <t>Casa Diseño</t>
   </si>
   <si>
+    <t>ClaveTemporal123</t>
+  </si>
+  <si>
     <t>si</t>
   </si>
   <si>
+    <t>María Soto</t>
+  </si>
+  <si>
+    <t>maria@empresa.cl</t>
+  </si>
+  <si>
     <t>produccion</t>
   </si>
   <si>
+    <t>ClaveTemporal456</t>
+  </si>
+  <si>
     <t>Cliente Demo</t>
   </si>
   <si>
@@ -65,6 +83,9 @@
     <t>Muebles Demo</t>
   </si>
   <si>
+    <t>ClaveTemporal789</t>
+  </si>
+  <si>
     <t>Perfil</t>
   </si>
   <si>
@@ -123,85 +144,13 @@
   </si>
   <si>
     <t>Use “si” para habilitar la cuenta o “no” para crearla desactivada.</t>
-  </si>
-  <si>
-    <t>ClaveTemporal3786</t>
-  </si>
-  <si>
-    <t>Paola Cofre</t>
-  </si>
-  <si>
-    <t>Francisca Guajardo</t>
-  </si>
-  <si>
-    <t>Pablo Yap</t>
-  </si>
-  <si>
-    <t>Geraldin Belmar</t>
-  </si>
-  <si>
-    <t>Pamela Valle</t>
-  </si>
-  <si>
-    <t>Fernanda Guajardo</t>
-  </si>
-  <si>
-    <t>Soledad Rozas</t>
-  </si>
-  <si>
-    <t>Fabricio Manriquez</t>
-  </si>
-  <si>
-    <t>Gerencia</t>
-  </si>
-  <si>
-    <t>mkt</t>
-  </si>
-  <si>
-    <t>pcofre@cdchile.cl</t>
-  </si>
-  <si>
-    <t>franguajardo@cdchile.cl</t>
-  </si>
-  <si>
-    <t>pyap@cdchile.cl</t>
-  </si>
-  <si>
-    <t>lbelmar@cdchile.cl</t>
-  </si>
-  <si>
-    <t>pvalle@cdchile.cl</t>
-  </si>
-  <si>
-    <t>fguajardo@cdchile.cl</t>
-  </si>
-  <si>
-    <t>srozas@cdchile.cl</t>
-  </si>
-  <si>
-    <t>Matias Nanjari</t>
-  </si>
-  <si>
-    <t>mnanjari@cdchile.cl</t>
-  </si>
-  <si>
-    <t>fmanriquez@cdchile.cl</t>
-  </si>
-  <si>
-    <t>contacto@cdchile.cl</t>
-  </si>
-  <si>
-    <t>mkt@cdchile.cl</t>
-  </si>
-  <si>
-    <t>CASADISEÑO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -215,16 +164,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF25313C"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -310,11 +249,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -334,12 +272,8 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -550,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -583,246 +517,65 @@
     </row>
     <row r="2" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>45</v>
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>46</v>
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>57</v>
+        <v>15</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2:C200" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"admin,comercial,produccion,cliente"</formula1>
@@ -831,20 +584,6 @@
       <formula1>"si,no"</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{DCE3D3B8-BBD6-490C-A89E-00ADE3E39B3B}"/>
-    <hyperlink ref="B3:B12" r:id="rId2" display="pcofre@cdchile.cl" xr:uid="{4EF882CE-4631-40DB-A59E-C702C30AF701}"/>
-    <hyperlink ref="B3" r:id="rId3" xr:uid="{873E31C5-35AA-4F4F-8DB6-F1337C98FF4C}"/>
-    <hyperlink ref="B4" r:id="rId4" xr:uid="{D30FD9F3-EAAE-4390-A611-FDC797C19F5C}"/>
-    <hyperlink ref="B5" r:id="rId5" xr:uid="{D9D43109-EAA1-43C6-82B3-017E2A99D8C8}"/>
-    <hyperlink ref="B6" r:id="rId6" xr:uid="{D7D209F9-72CF-476D-A6E1-95AC46560B5D}"/>
-    <hyperlink ref="B7" r:id="rId7" xr:uid="{A041DECF-3116-4C6F-8CFE-F30DBBD45D34}"/>
-    <hyperlink ref="B8" r:id="rId8" xr:uid="{3DFE3D73-5FED-4D3D-ABF0-B4BB869E3C68}"/>
-    <hyperlink ref="B9" r:id="rId9" xr:uid="{375E8A27-6368-4E54-8184-310F80EBFC19}"/>
-    <hyperlink ref="B10" r:id="rId10" xr:uid="{0C65D528-A62B-41A2-A3D3-1FEBBC4DB75F}"/>
-    <hyperlink ref="B11" r:id="rId11" xr:uid="{6FA28ABB-3D56-409A-957F-9E174BC5B533}"/>
-    <hyperlink ref="B12" r:id="rId12" xr:uid="{7CAECD66-4D7D-4100-8898-51C7276C27D1}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -861,82 +600,82 @@
   <sheetData>
     <row r="1" spans="1:3" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
     </row>
     <row r="8" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
